--- a/data/trans_orig/IP19C01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53466</t>
+          <t>53703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50611</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64374</t>
+          <t>63897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94795</t>
+          <t>94857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114410</t>
+          <t>114596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63066</t>
+          <t>63004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66122</t>
+          <t>67198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81112</t>
+          <t>82165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72914</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88421</t>
+          <t>87888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143897</t>
+          <t>144694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165482</t>
+          <t>165469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>27896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>42863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56210</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77795</t>
+          <t>76998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54951</t>
+          <t>54447</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49839</t>
+          <t>50174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61818</t>
+          <t>62388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98145</t>
+          <t>97178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114457</t>
+          <t>114026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14257</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32620</t>
+          <t>33051</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48932</t>
+          <t>49899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52448</t>
+          <t>51858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68182</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54810</t>
+          <t>54520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68735</t>
+          <t>69304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111112</t>
+          <t>111094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134130</t>
+          <t>132020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>35523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51902</t>
+          <t>54012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74920</t>
+          <t>74938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217367</t>
+          <t>216587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>245325</t>
+          <t>244928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>244598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>271292</t>
+          <t>271064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>470844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>509320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105605</t>
+          <t>106002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133563</t>
+          <t>134343</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90439</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116908</t>
+          <t>117133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201113</t>
+          <t>203341</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242436</t>
+          <t>241817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>49534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>62780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>42489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56153</t>
+          <t>56636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98149</t>
+          <t>97254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116349</t>
+          <t>116313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33476</t>
+          <t>33532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35084</t>
+          <t>35120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64080</t>
+          <t>65322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80556</t>
+          <t>80490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83311</t>
+          <t>83426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97264</t>
+          <t>97166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152202</t>
+          <t>152259</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174522</t>
+          <t>174095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,38%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32043</t>
+          <t>32109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53400</t>
+          <t>53827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75720</t>
+          <t>75663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61522</t>
+          <t>62081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50316</t>
+          <t>50678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63193</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,47 +3416,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>79,47%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>113836</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>104700</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>122661</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>73,54%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>67,64%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>79,24%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>113836</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>104501</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>122352</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>73,54%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>67,51%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,47 +3529,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>20,53%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>36,46%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>40951</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>32126</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>50087</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>26,46%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>40951</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>32435</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>50286</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62620</t>
+          <t>62387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77138</t>
+          <t>77459</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73029</t>
+          <t>74016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86278</t>
+          <t>86135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141153</t>
+          <t>141169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160340</t>
+          <t>161445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30357</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>27832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48124</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>243057</t>
+          <t>243040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269024</t>
+          <t>270963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264985</t>
+          <t>264906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292453</t>
+          <t>292529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516222</t>
+          <t>516752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>555101</t>
+          <t>553917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86997</t>
+          <t>85058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112964</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102412</t>
+          <t>102491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168317</t>
+          <t>169501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207196</t>
+          <t>206666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>39677</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53693</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55217</t>
+          <t>54860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>67225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99643</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117914</t>
+          <t>117480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30666</t>
+          <t>31164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>48872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67264</t>
+          <t>67262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82419</t>
+          <t>82280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69977</t>
+          <t>70552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>85553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142905</t>
+          <t>143319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164076</t>
+          <t>163701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40697</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23388</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52477</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73648</t>
+          <t>73234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63769</t>
+          <t>64172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>49230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62022</t>
+          <t>62411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105966</t>
+          <t>106203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123720</t>
+          <t>124074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22951</t>
+          <t>23283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30017</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47771</t>
+          <t>47534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79891</t>
+          <t>78086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94003</t>
+          <t>93968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91683</t>
+          <t>91803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161433</t>
+          <t>162941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182252</t>
+          <t>182661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29595</t>
+          <t>29618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>55043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253328</t>
+          <t>254511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282120</t>
+          <t>283010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267518</t>
+          <t>268115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294469</t>
+          <t>294193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>529969</t>
+          <t>530285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>569772</t>
+          <t>568634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82904</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111696</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76933</t>
+          <t>77209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103884</t>
+          <t>103287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166653</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206456</t>
+          <t>206140</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>50012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>61800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64828</t>
+          <t>65180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79546</t>
+          <t>79101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119639</t>
+          <t>120659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138262</t>
+          <t>139066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>34356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90905</t>
+          <t>90938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104233</t>
+          <t>104009</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120371</t>
+          <t>119924</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140936</t>
+          <t>140475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>217001</t>
+          <t>215931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242212</t>
+          <t>240512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>22795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>26901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>47452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>40597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>65178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66943</t>
+          <t>65824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85503</t>
+          <t>84802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86843</t>
+          <t>85605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104403</t>
+          <t>104002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157379</t>
+          <t>158128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184021</t>
+          <t>184233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40012</t>
+          <t>41131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33404</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>42969</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69823</t>
+          <t>69074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81606</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93010</t>
+          <t>93080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89533</t>
+          <t>88784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103044</t>
+          <t>102976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175832</t>
+          <t>175435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193931</t>
+          <t>193582</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18820</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36919</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>305727</t>
+          <t>304341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332886</t>
+          <t>332207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>379470</t>
+          <t>381145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>414420</t>
+          <t>414784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>694445</t>
+          <t>696742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>738683</t>
+          <t>739765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58747</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85906</t>
+          <t>87292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104974</t>
+          <t>103299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137393</t>
+          <t>136311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181631</t>
+          <t>179334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57894</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50923</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>64615</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>61,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>47353</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39894</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53703</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>40154</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54111</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57894</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>50727</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>63897</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94857</t>
+          <t>94036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114596</t>
+          <t>113994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24294</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17573</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31265</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28320</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21970</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35779</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21562</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35519</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24294</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18291</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31461</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43265</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63004</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81141</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>73352</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>88019</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>65,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>74485</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>67198</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>82165</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>66550</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>81851</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>67,68%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>81141</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>73762</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>87888</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,69%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144694</t>
+          <t>144541</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165469</t>
+          <t>166008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30490</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23612</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38279</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>35576</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27896</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42863</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28210</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>43511</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30490</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23743</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37869</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56223</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76998</t>
+          <t>77151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56876</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50456</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62696</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>49486</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42984</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54447</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43397</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54539</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>71,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56876</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>50174</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62388</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97178</t>
+          <t>98080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114026</t>
+          <t>115321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20993</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27413</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19722</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14761</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26224</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>14669</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25811</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>28,5%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20993</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15481</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27695</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33051</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49899</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62309</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>54632</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69615</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>60895</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51858</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>68882</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52207</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>69328</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>63,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>62309</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>54520</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>69304</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>69,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111094</t>
+          <t>111958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>132812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27734</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20428</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35411</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>30,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35094</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27107</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>44131</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26661</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>43782</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>36,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27734</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35523</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54012</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74938</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>244477</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>272001</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>232218</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>216587</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>244928</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>215484</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>244818</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>258220</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>244598</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>271064</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470844</t>
+          <t>469582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>509320</t>
+          <t>510472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>103511</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89730</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>117254</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118712</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106002</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>134343</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>106112</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>135446</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>103511</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>90667</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>117133</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203341</t>
+          <t>202189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241817</t>
+          <t>243079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50274</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43621</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57211</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>56853</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49534</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>62780</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>50036</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>63095</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>75,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>50274</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>42489</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>56636</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>66,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97254</t>
+          <t>97208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116313</t>
+          <t>115729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25747</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18810</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32400</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18558</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25877</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12316</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25375</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25747</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19385</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>33532</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54179</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76021</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76021</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76021</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75411</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75411</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75411</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76021</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76021</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>90670</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83076</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>97336</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>84,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>72811</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>65322</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>80490</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>63713</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>80328</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>64,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>90670</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83426</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>97166</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>78,62%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152259</t>
+          <t>152302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174095</t>
+          <t>173441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32246</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>39788</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32109</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47277</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32271</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>48886</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>35,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24652</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18156</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>31896</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,38%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53827</t>
+          <t>54481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75663</t>
+          <t>75620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115322</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115322</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115322</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>115322</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>115322</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>115322</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57501</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50237</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>63426</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>62,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>56335</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62081</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>49292</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>61710</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57501</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>50678</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>63380</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104700</t>
+          <t>104620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122661</t>
+          <t>122289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22252</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16327</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29516</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18699</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12953</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25053</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13324</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25742</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>24,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22252</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>16373</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>29075</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32126</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50087</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75034</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75034</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75034</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>80687</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75120</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>86345</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>70793</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>62387</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>77459</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62811</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>77755</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>76,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>80687</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>74016</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>86135</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141169</t>
+          <t>141405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161445</t>
+          <t>160230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15614</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9956</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21181</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>22184</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15518</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30590</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15222</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30166</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>15614</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10166</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22285</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48108</t>
+          <t>47872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>264423</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>291726</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>363</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>256792</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>243040</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>270963</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>241589</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>269703</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>279132</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>264906</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>292529</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516752</t>
+          <t>516958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>553917</t>
+          <t>554768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>88265</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75671</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>102974</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>99229</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>85058</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112981</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>86318</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>114432</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>88265</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>74868</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>102491</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169501</t>
+          <t>168650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206666</t>
+          <t>206460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>356021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>356021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>356021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61892</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54830</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66930</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>47394</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39677</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52860</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39821</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53527</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>66,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>61892</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>54860</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>67225</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>80,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>99932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117480</t>
+          <t>118185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15418</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10380</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22480</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23447</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17981</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31164</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17314</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31020</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,1%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15418</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10085</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22450</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,94%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48872</t>
+          <t>48219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>77310</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77310</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77310</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>77310</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>77310</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>77310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78290</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70199</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>85358</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>75244</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>67262</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>82280</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>67089</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>82557</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>69,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>78290</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>70552</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>85553</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143319</t>
+          <t>140488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163701</t>
+          <t>162565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30302</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23234</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38393</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>32717</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25681</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40699</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25404</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40872</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>30,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30302</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23039</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38040</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>53988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73234</t>
+          <t>76065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107961</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107961</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107961</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56288</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49430</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61803</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>59010</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52305</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64172</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52997</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>64447</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56288</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>49230</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62411</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106203</t>
+          <t>106723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124074</t>
+          <t>123167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21862</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28720</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16578</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11416</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23283</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11141</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22591</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21862</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15739</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>28920</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29663</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47534</t>
+          <t>47014</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>78150</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>78150</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>78150</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>78150</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>78150</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>78150</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>85503</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>77555</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91782</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>86919</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>78086</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>93968</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>78539</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>93626</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>78,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>70,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>85503</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>77732</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>91803</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162941</t>
+          <t>161214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182661</t>
+          <t>182040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21847</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29795</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23715</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16666</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32548</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17008</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>32095</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>21,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>15547</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29618</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>35944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>107350</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>107350</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>107350</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>110634</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>110634</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>110634</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>107350</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>107350</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>107350</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>268126</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>295931</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>72,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>386</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>268568</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>254511</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>283010</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>254062</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>282940</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>281974</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>268115</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>294193</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>530285</t>
+          <t>530895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>568634</t>
+          <t>569710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>89428</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75471</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>103276</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>96456</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>82014</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>110513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>82084</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>110962</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>89428</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>77209</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>103287</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167791</t>
+          <t>166715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206140</t>
+          <t>205530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>530</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>365024</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>365024</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>365024</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>70905</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63261</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75825</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>56586</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>50012</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>61800</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>81,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>88,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>60321</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>53040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79101</t>
+          <t>65655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>130212</t>
+          <t>131226</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120659</t>
+          <t>121316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139066</t>
+          <t>138771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10552</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5632</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18196</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13180</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7966</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19754</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>24509</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>128289</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>117024</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>136929</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>98574</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>90938</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>104009</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>86,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>131887</t>
+          <t>101067</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119924</t>
+          <t>92723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140475</t>
+          <t>107008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>230460</t>
+          <t>229355</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215931</t>
+          <t>215968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240512</t>
+          <t>241378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34041</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25401</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45306</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15159</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9724</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22795</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26901</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47452</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>50649</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40597</t>
+          <t>37938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65178</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88925</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78122</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>97197</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>79,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>69,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>76419</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65824</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>84802</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>71,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>96507</t>
+          <t>73522</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85605</t>
+          <t>65297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104002</t>
+          <t>81193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>172926</t>
+          <t>162448</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158128</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184233</t>
+          <t>174032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23173</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33976</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30536</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22153</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>41131</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28,55%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>54276</t>
+          <t>52089</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42969</t>
+          <t>40505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69074</t>
+          <t>64588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88287</t>
+          <t>92538</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81333</t>
+          <t>84990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93080</t>
+          <t>97416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>89500</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88784</t>
+          <t>81771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102976</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>185541</t>
+          <t>182038</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175435</t>
+          <t>173404</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193582</t>
+          <t>189339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12671</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20219</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12892</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8099</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19846</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>27210</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>18445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37316</t>
+          <t>34380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>362215</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>394644</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>78,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>319866</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>304341</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>332207</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>399272</t>
+          <t>324410</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>381145</t>
+          <t>310839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>414784</t>
+          <t>337298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>719137</t>
+          <t>705067</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>696742</t>
+          <t>684521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>739765</t>
+          <t>725196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80437</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>66451</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>98880</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>71767</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>59426</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>87292</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85172</t>
+          <t>71868</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69660</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>85439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>156939</t>
+          <t>152305</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>132176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179334</t>
+          <t>172851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
